--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N74_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N74_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.38993021478494</v>
+        <v>3.963363659902553</v>
       </c>
       <c r="D2" t="n">
-        <v>24.55665882109002</v>
+        <v>3.990457058427129</v>
       </c>
       <c r="E2" t="n">
-        <v>5.372909396819088</v>
+        <v>0.8730977769831016</v>
       </c>
       <c r="F2" t="n">
-        <v>5.261940895740873</v>
+        <v>0.855065395557892</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.55461030992274</v>
+        <v>4.477624175362446</v>
       </c>
       <c r="D3" t="n">
-        <v>27.72098781297829</v>
+        <v>4.504660519608973</v>
       </c>
       <c r="E3" t="n">
-        <v>5.372909396819088</v>
+        <v>0.8730977769831016</v>
       </c>
       <c r="F3" t="n">
-        <v>5.261940895740873</v>
+        <v>0.855065395557892</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.90902936465575</v>
+        <v>2.422717271756559</v>
       </c>
       <c r="D4" t="n">
-        <v>15.31817798140201</v>
+        <v>2.489203921977827</v>
       </c>
       <c r="E4" t="n">
-        <v>5.372909396819088</v>
+        <v>0.8730977769831016</v>
       </c>
       <c r="F4" t="n">
-        <v>5.261940895740873</v>
+        <v>0.855065395557892</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
